--- a/data/nzd0077/nzd0077.xlsx
+++ b/data/nzd0077/nzd0077.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K351"/>
+  <dimension ref="A1:K352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14133,6 +14133,45 @@
         <v>365.78</v>
       </c>
       <c r="K351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>316.43</v>
+      </c>
+      <c r="C352" t="n">
+        <v>326.17</v>
+      </c>
+      <c r="D352" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="E352" t="n">
+        <v>333.7</v>
+      </c>
+      <c r="F352" t="n">
+        <v>337.51</v>
+      </c>
+      <c r="G352" t="n">
+        <v>347.08</v>
+      </c>
+      <c r="H352" t="n">
+        <v>348.27</v>
+      </c>
+      <c r="I352" t="n">
+        <v>363.93</v>
+      </c>
+      <c r="J352" t="n">
+        <v>363.87</v>
+      </c>
+      <c r="K352" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14149,7 +14188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17762,6 +17801,16 @@
       </c>
       <c r="B361" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -17930,28 +17979,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1476668294093153</v>
+        <v>0.14456733877525</v>
       </c>
       <c r="J2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05675458828664259</v>
+        <v>0.05464591308505551</v>
       </c>
       <c r="M2" t="n">
-        <v>3.488423199677075</v>
+        <v>3.494112355598658</v>
       </c>
       <c r="N2" t="n">
-        <v>20.28869256692867</v>
+        <v>20.31433772547029</v>
       </c>
       <c r="O2" t="n">
-        <v>4.504297122407521</v>
+        <v>4.507142967054661</v>
       </c>
       <c r="P2" t="n">
-        <v>317.9062748800213</v>
+        <v>317.9391698364227</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18008,28 +18057,28 @@
         <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1627224699106184</v>
+        <v>0.1600659405347194</v>
       </c>
       <c r="J3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08690243918817975</v>
+        <v>0.08451934543343109</v>
       </c>
       <c r="M3" t="n">
-        <v>3.066165369384415</v>
+        <v>3.070835764340059</v>
       </c>
       <c r="N3" t="n">
-        <v>15.57559724999521</v>
+        <v>15.59252268092397</v>
       </c>
       <c r="O3" t="n">
-        <v>3.946593119387304</v>
+        <v>3.948736846248933</v>
       </c>
       <c r="P3" t="n">
-        <v>326.4620688747435</v>
+        <v>326.4902626744083</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18086,28 +18135,28 @@
         <v>0.0862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08366925800054245</v>
+        <v>0.08135056141473487</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02765999576822631</v>
+        <v>0.0262657592058384</v>
       </c>
       <c r="M4" t="n">
-        <v>2.863751379467585</v>
+        <v>2.865696910181375</v>
       </c>
       <c r="N4" t="n">
-        <v>13.77724295618158</v>
+        <v>13.78469205569519</v>
       </c>
       <c r="O4" t="n">
-        <v>3.711770865258465</v>
+        <v>3.712774172461232</v>
       </c>
       <c r="P4" t="n">
-        <v>328.6979452924119</v>
+        <v>328.7225536658847</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18164,28 +18213,28 @@
         <v>0.0814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1224427988433716</v>
+        <v>0.1214965319761483</v>
       </c>
       <c r="J5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0689694945670748</v>
+        <v>0.06834558659173862</v>
       </c>
       <c r="M5" t="n">
-        <v>2.373535744802092</v>
+        <v>2.371867378747414</v>
       </c>
       <c r="N5" t="n">
-        <v>11.33020588259501</v>
+        <v>11.30570396930294</v>
       </c>
       <c r="O5" t="n">
-        <v>3.366037118422049</v>
+        <v>3.362395570021905</v>
       </c>
       <c r="P5" t="n">
-        <v>332.0706174947779</v>
+        <v>332.0806602440604</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18242,28 +18291,28 @@
         <v>0.0896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1399341292519782</v>
+        <v>0.1396415513946156</v>
       </c>
       <c r="J6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07062560641358151</v>
+        <v>0.07077078853005836</v>
       </c>
       <c r="M6" t="n">
-        <v>2.613089273435669</v>
+        <v>2.607347644799182</v>
       </c>
       <c r="N6" t="n">
-        <v>14.42581137953661</v>
+        <v>14.38545576286748</v>
       </c>
       <c r="O6" t="n">
-        <v>3.798132617423542</v>
+        <v>3.792816336558821</v>
       </c>
       <c r="P6" t="n">
-        <v>334.2684812505711</v>
+        <v>334.2715863852524</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18320,28 +18369,28 @@
         <v>0.1002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2753372317443112</v>
+        <v>0.2770677553970348</v>
       </c>
       <c r="J7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2635038354754498</v>
+        <v>0.2667735444170278</v>
       </c>
       <c r="M7" t="n">
-        <v>2.572503561540063</v>
+        <v>2.573056112729782</v>
       </c>
       <c r="N7" t="n">
-        <v>11.86254489631827</v>
+        <v>11.85476137389581</v>
       </c>
       <c r="O7" t="n">
-        <v>3.44420453752652</v>
+        <v>3.44307440725521</v>
       </c>
       <c r="P7" t="n">
-        <v>336.6463667006482</v>
+        <v>336.628000618337</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18398,28 +18447,28 @@
         <v>0.0829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2944981540669306</v>
+        <v>0.2956117988770115</v>
       </c>
       <c r="J8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.323560765258454</v>
+        <v>0.3263977244104485</v>
       </c>
       <c r="M8" t="n">
-        <v>2.317659541438992</v>
+        <v>2.315919555080036</v>
       </c>
       <c r="N8" t="n">
-        <v>10.15085272604955</v>
+        <v>10.13270568099683</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18604028945799</v>
+        <v>3.183191116002435</v>
       </c>
       <c r="P8" t="n">
-        <v>338.4102832595075</v>
+        <v>338.398464124753</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18476,28 +18525,28 @@
         <v>0.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3482241444349787</v>
+        <v>0.3501193201732146</v>
       </c>
       <c r="J9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3612880117750558</v>
+        <v>0.3646868520111627</v>
       </c>
       <c r="M9" t="n">
-        <v>2.594296588653475</v>
+        <v>2.596061584105696</v>
       </c>
       <c r="N9" t="n">
-        <v>12.00144982897427</v>
+        <v>11.99845609123192</v>
       </c>
       <c r="O9" t="n">
-        <v>3.464310873604485</v>
+        <v>3.463878763933853</v>
       </c>
       <c r="P9" t="n">
-        <v>351.2525918320072</v>
+        <v>351.2324782938028</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18554,28 +18603,28 @@
         <v>0.1184</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2946145368636229</v>
+        <v>0.2987808829223232</v>
       </c>
       <c r="J10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3104669349038756</v>
+        <v>0.3148981384892575</v>
       </c>
       <c r="M10" t="n">
-        <v>2.584391260629148</v>
+        <v>2.598576950851125</v>
       </c>
       <c r="N10" t="n">
-        <v>10.79226308964774</v>
+        <v>10.91229613142639</v>
       </c>
       <c r="O10" t="n">
-        <v>3.285158000712864</v>
+        <v>3.30337647437079</v>
       </c>
       <c r="P10" t="n">
-        <v>348.6519750656092</v>
+        <v>348.6077575511415</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18613,7 +18662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K351"/>
+  <dimension ref="A1:K352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38623,6 +38672,63 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-35.447117845255846,174.42718781248374</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-35.4478603683277,174.426847629799</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-35.44865339081947,174.42672050666678</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-35.44940416989014,174.42674657652623</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-35.45014421321034,174.42678057878726</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-35.45088338078386,174.42689805048747</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-35.45161667275857,174.42702140769066</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-35.45232185450439,174.4273100573513</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-35.453006419018045,174.4276233703082</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0077/nzd0077.xlsx
+++ b/data/nzd0077/nzd0077.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K352"/>
+  <dimension ref="A1:K355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14174,6 +14174,123 @@
       <c r="K352" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>314.45</v>
+      </c>
+      <c r="C353" t="n">
+        <v>327.61</v>
+      </c>
+      <c r="D353" t="n">
+        <v>326.76</v>
+      </c>
+      <c r="E353" t="n">
+        <v>334.07</v>
+      </c>
+      <c r="F353" t="n">
+        <v>337.34</v>
+      </c>
+      <c r="G353" t="n">
+        <v>345.5</v>
+      </c>
+      <c r="H353" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="I353" t="n">
+        <v>363.06</v>
+      </c>
+      <c r="J353" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>314.34</v>
+      </c>
+      <c r="C354" t="n">
+        <v>328.09</v>
+      </c>
+      <c r="D354" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="E354" t="n">
+        <v>334.08</v>
+      </c>
+      <c r="F354" t="n">
+        <v>336.99</v>
+      </c>
+      <c r="G354" t="n">
+        <v>345.73</v>
+      </c>
+      <c r="H354" t="n">
+        <v>346.74</v>
+      </c>
+      <c r="I354" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="J354" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>314.15</v>
+      </c>
+      <c r="C355" t="n">
+        <v>328.09</v>
+      </c>
+      <c r="D355" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="E355" t="n">
+        <v>334.08</v>
+      </c>
+      <c r="F355" t="n">
+        <v>336.99</v>
+      </c>
+      <c r="G355" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="H355" t="n">
+        <v>346.74</v>
+      </c>
+      <c r="I355" t="n">
+        <v>367.65</v>
+      </c>
+      <c r="J355" t="n">
+        <v>364.19</v>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -14188,7 +14305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B362"/>
+  <dimension ref="A1:B365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17811,6 +17928,36 @@
       </c>
       <c r="B362" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -17979,28 +18126,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.14456733877525</v>
+        <v>0.1319623163902916</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05464591308505551</v>
+        <v>0.04578874844716307</v>
       </c>
       <c r="M2" t="n">
-        <v>3.494112355598658</v>
+        <v>3.528325545985873</v>
       </c>
       <c r="N2" t="n">
-        <v>20.31433772547029</v>
+        <v>20.60833230025776</v>
       </c>
       <c r="O2" t="n">
-        <v>4.507142967054661</v>
+        <v>4.53964010690911</v>
       </c>
       <c r="P2" t="n">
-        <v>317.9391698364227</v>
+        <v>318.0734360363797</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18057,28 +18204,28 @@
         <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1600659405347194</v>
+        <v>0.1552503651868567</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08451934543343109</v>
+        <v>0.08100241038774048</v>
       </c>
       <c r="M3" t="n">
-        <v>3.070835764340059</v>
+        <v>3.068802948887038</v>
       </c>
       <c r="N3" t="n">
-        <v>15.59252268092397</v>
+        <v>15.52883654119043</v>
       </c>
       <c r="O3" t="n">
-        <v>3.948736846248933</v>
+        <v>3.940664479651932</v>
       </c>
       <c r="P3" t="n">
-        <v>326.4902626744083</v>
+        <v>326.5415539938807</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18135,28 +18282,28 @@
         <v>0.0862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08135056141473487</v>
+        <v>0.07478461107643954</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0262657592058384</v>
+        <v>0.02250546289282351</v>
       </c>
       <c r="M4" t="n">
-        <v>2.865696910181375</v>
+        <v>2.870493404030155</v>
       </c>
       <c r="N4" t="n">
-        <v>13.78469205569519</v>
+        <v>13.79456772122601</v>
       </c>
       <c r="O4" t="n">
-        <v>3.712774172461232</v>
+        <v>3.714103892088374</v>
       </c>
       <c r="P4" t="n">
-        <v>328.7225536658847</v>
+        <v>328.7924900838557</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18213,28 +18360,28 @@
         <v>0.0814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1214965319761483</v>
+        <v>0.1193497042047119</v>
       </c>
       <c r="J5" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06834558659173862</v>
+        <v>0.06722804917694492</v>
       </c>
       <c r="M5" t="n">
-        <v>2.371867378747414</v>
+        <v>2.363144897739997</v>
       </c>
       <c r="N5" t="n">
-        <v>11.30570396930294</v>
+        <v>11.22341161201027</v>
       </c>
       <c r="O5" t="n">
-        <v>3.362395570021905</v>
+        <v>3.350136058731089</v>
       </c>
       <c r="P5" t="n">
-        <v>332.0806602440604</v>
+        <v>332.1035275198939</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18291,28 +18438,28 @@
         <v>0.0896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1396415513946156</v>
+        <v>0.1380884640701778</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07077078853005836</v>
+        <v>0.0705275532065035</v>
       </c>
       <c r="M6" t="n">
-        <v>2.607347644799182</v>
+        <v>2.594218099249955</v>
       </c>
       <c r="N6" t="n">
-        <v>14.38545576286748</v>
+        <v>14.27084630160423</v>
       </c>
       <c r="O6" t="n">
-        <v>3.792816336558821</v>
+        <v>3.777677368649185</v>
       </c>
       <c r="P6" t="n">
-        <v>334.2715863852524</v>
+        <v>334.288131287729</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18369,28 +18516,28 @@
         <v>0.1002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2770677553970348</v>
+        <v>0.2793596241081586</v>
       </c>
       <c r="J7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2667735444170278</v>
+        <v>0.2735361406371104</v>
       </c>
       <c r="M7" t="n">
-        <v>2.573056112729782</v>
+        <v>2.561890467305508</v>
       </c>
       <c r="N7" t="n">
-        <v>11.85476137389581</v>
+        <v>11.7701988915875</v>
       </c>
       <c r="O7" t="n">
-        <v>3.44307440725521</v>
+        <v>3.430772346219944</v>
       </c>
       <c r="P7" t="n">
-        <v>336.628000618337</v>
+        <v>336.6035904040382</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18447,28 +18594,28 @@
         <v>0.0829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2956117988770115</v>
+        <v>0.2961645186711787</v>
       </c>
       <c r="J8" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K8" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3263977244104485</v>
+        <v>0.3314345335511397</v>
       </c>
       <c r="M8" t="n">
-        <v>2.315919555080036</v>
+        <v>2.29866505499015</v>
       </c>
       <c r="N8" t="n">
-        <v>10.13270568099683</v>
+        <v>10.047764922022</v>
       </c>
       <c r="O8" t="n">
-        <v>3.183191116002435</v>
+        <v>3.169820960562599</v>
       </c>
       <c r="P8" t="n">
-        <v>338.398464124753</v>
+        <v>338.3925760152061</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18525,28 +18672,28 @@
         <v>0.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3501193201732146</v>
+        <v>0.3567035341435745</v>
       </c>
       <c r="J9" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K9" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3646868520111627</v>
+        <v>0.3746014075173753</v>
       </c>
       <c r="M9" t="n">
-        <v>2.596061584105696</v>
+        <v>2.60554711088801</v>
       </c>
       <c r="N9" t="n">
-        <v>11.99845609123192</v>
+        <v>12.06311719055383</v>
       </c>
       <c r="O9" t="n">
-        <v>3.463878763933853</v>
+        <v>3.473199848922291</v>
       </c>
       <c r="P9" t="n">
-        <v>351.2324782938028</v>
+        <v>351.1623202377515</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18603,28 +18750,28 @@
         <v>0.1184</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2987808829223232</v>
+        <v>0.3104915878555122</v>
       </c>
       <c r="J10" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K10" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3148981384892575</v>
+        <v>0.3278638904907327</v>
       </c>
       <c r="M10" t="n">
-        <v>2.598576950851125</v>
+        <v>2.637324068389688</v>
       </c>
       <c r="N10" t="n">
-        <v>10.91229613142639</v>
+        <v>11.22329928904338</v>
       </c>
       <c r="O10" t="n">
-        <v>3.30337647437079</v>
+        <v>3.35011929474808</v>
       </c>
       <c r="P10" t="n">
-        <v>348.6077575511415</v>
+        <v>348.4830148915514</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18662,7 +18809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K352"/>
+  <dimension ref="A1:K355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38729,6 +38876,177 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-35.44710987449687,174.4271682950859</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-35.447864110115894,174.42686282068794</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-35.448653301580215,174.42671918914317</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-35.44940424103036,174.42675065189428</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-35.450144231051645,174.4267787060046</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-35.45088447628065,174.4268806948485</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-35.45161871836715,174.42700317941006</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-35.452323824314135,174.4273007794411</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-35.45300784061784,174.4276188446423</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-35.44710943167683,174.42716721078614</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-35.44786535737819,174.4268678843179</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-35.44865356186135,174.42672303192032</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-35.44940424295306,174.42675076203938</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-35.45014426778365,174.42677485027556</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-35.450884316809756,174.42688322130232</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-35.45161854687911,174.42700470752942</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-35.45232380167265,174.42730088608377</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-35.453008260635926,174.4276175075137</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-35.44710866680582,174.42716533790474</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-35.44786535737819,174.4268678843179</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-35.44865356186135,174.42672303192032</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-35.44940424295306,174.42675076203938</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-35.45014426778365,174.42677485027556</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-35.45088471895364,174.42687685024487</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-35.45161854687911,174.42700470752942</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-35.45231343186164,174.42734972841018</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-35.453005385127206,174.42762666170148</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0077/nzd0077.xlsx
+++ b/data/nzd0077/nzd0077.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K355"/>
+  <dimension ref="A1:K357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14289,6 +14289,84 @@
         <v>364.19</v>
       </c>
       <c r="K355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>315.37</v>
+      </c>
+      <c r="C356" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="D356" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="E356" t="n">
+        <v>334.88</v>
+      </c>
+      <c r="F356" t="n">
+        <v>337.9</v>
+      </c>
+      <c r="G356" t="n">
+        <v>345.27</v>
+      </c>
+      <c r="H356" t="n">
+        <v>348.31</v>
+      </c>
+      <c r="I356" t="n">
+        <v>368.24</v>
+      </c>
+      <c r="J356" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>316.62</v>
+      </c>
+      <c r="C357" t="n">
+        <v>331.02</v>
+      </c>
+      <c r="D357" t="n">
+        <v>329.33</v>
+      </c>
+      <c r="E357" t="n">
+        <v>336.33</v>
+      </c>
+      <c r="F357" t="n">
+        <v>340.09</v>
+      </c>
+      <c r="G357" t="n">
+        <v>346.48</v>
+      </c>
+      <c r="H357" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="I357" t="n">
+        <v>372.31</v>
+      </c>
+      <c r="J357" t="n">
+        <v>365.51</v>
+      </c>
+      <c r="K357" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -14305,7 +14383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B365"/>
+  <dimension ref="A1:B367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17958,6 +18036,26 @@
       </c>
       <c r="B365" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -18126,28 +18224,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1319623163902916</v>
+        <v>0.1257127783845604</v>
       </c>
       <c r="J2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04578874844716307</v>
+        <v>0.04189040235265573</v>
       </c>
       <c r="M2" t="n">
-        <v>3.528325545985873</v>
+        <v>3.541354571250756</v>
       </c>
       <c r="N2" t="n">
-        <v>20.60833230025776</v>
+        <v>20.67057714685786</v>
       </c>
       <c r="O2" t="n">
-        <v>4.53964010690911</v>
+        <v>4.546490640797345</v>
       </c>
       <c r="P2" t="n">
-        <v>318.0734360363797</v>
+        <v>318.140275425118</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18204,28 +18302,28 @@
         <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1552503651868567</v>
+        <v>0.1543975749363075</v>
       </c>
       <c r="J3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08100241038774048</v>
+        <v>0.08107667411865327</v>
       </c>
       <c r="M3" t="n">
-        <v>3.068802948887038</v>
+        <v>3.057400348829713</v>
       </c>
       <c r="N3" t="n">
-        <v>15.52883654119043</v>
+        <v>15.45102853053183</v>
       </c>
       <c r="O3" t="n">
-        <v>3.940664479651932</v>
+        <v>3.930779633931649</v>
       </c>
       <c r="P3" t="n">
-        <v>326.5415539938807</v>
+        <v>326.5506694155189</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18282,28 +18380,28 @@
         <v>0.0862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07478461107643954</v>
+        <v>0.07282197065440645</v>
       </c>
       <c r="J4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02250546289282351</v>
+        <v>0.02160268862971071</v>
       </c>
       <c r="M4" t="n">
-        <v>2.870493404030155</v>
+        <v>2.863083721437754</v>
       </c>
       <c r="N4" t="n">
-        <v>13.79456772122601</v>
+        <v>13.73489657272104</v>
       </c>
       <c r="O4" t="n">
-        <v>3.714103892088374</v>
+        <v>3.706062138270356</v>
       </c>
       <c r="P4" t="n">
-        <v>328.7924900838557</v>
+        <v>328.8134801733161</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18360,28 +18458,28 @@
         <v>0.0814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1193497042047119</v>
+        <v>0.1196539764672768</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06722804917694492</v>
+        <v>0.06832823402164412</v>
       </c>
       <c r="M5" t="n">
-        <v>2.363144897739997</v>
+        <v>2.353885123041826</v>
       </c>
       <c r="N5" t="n">
-        <v>11.22341161201027</v>
+        <v>11.163750058646</v>
       </c>
       <c r="O5" t="n">
-        <v>3.350136058731089</v>
+        <v>3.341219845901493</v>
       </c>
       <c r="P5" t="n">
-        <v>332.1035275198939</v>
+        <v>332.1002691601025</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18438,28 +18536,28 @@
         <v>0.0896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1380884640701778</v>
+        <v>0.1391690205818968</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0705275532065035</v>
+        <v>0.07234285782865379</v>
       </c>
       <c r="M6" t="n">
-        <v>2.594218099249955</v>
+        <v>2.585035511424944</v>
       </c>
       <c r="N6" t="n">
-        <v>14.27084630160423</v>
+        <v>14.202672325072</v>
       </c>
       <c r="O6" t="n">
-        <v>3.777677368649185</v>
+        <v>3.76864330032334</v>
       </c>
       <c r="P6" t="n">
-        <v>334.288131287729</v>
+        <v>334.276568061296</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18516,28 +18614,28 @@
         <v>0.1002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2793596241081586</v>
+        <v>0.281265618684236</v>
       </c>
       <c r="J7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2735361406371104</v>
+        <v>0.2784626407858656</v>
       </c>
       <c r="M7" t="n">
-        <v>2.561890467305508</v>
+        <v>2.556497837428176</v>
       </c>
       <c r="N7" t="n">
-        <v>11.7701988915875</v>
+        <v>11.72244694082184</v>
       </c>
       <c r="O7" t="n">
-        <v>3.430772346219944</v>
+        <v>3.423805914595896</v>
       </c>
       <c r="P7" t="n">
-        <v>336.6035904040382</v>
+        <v>336.5832012962645</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18594,28 +18692,28 @@
         <v>0.0829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2961645186711787</v>
+        <v>0.2993826037657673</v>
       </c>
       <c r="J8" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3314345335511397</v>
+        <v>0.3378983530434641</v>
       </c>
       <c r="M8" t="n">
-        <v>2.29866505499015</v>
+        <v>2.2995187891294</v>
       </c>
       <c r="N8" t="n">
-        <v>10.047764922022</v>
+        <v>10.04349365963388</v>
       </c>
       <c r="O8" t="n">
-        <v>3.169820960562599</v>
+        <v>3.169147150202066</v>
       </c>
       <c r="P8" t="n">
-        <v>338.3925760152061</v>
+        <v>338.3581511004917</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18672,28 +18770,28 @@
         <v>0.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3567035341435745</v>
+        <v>0.3671833364445143</v>
       </c>
       <c r="J9" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3746014075173753</v>
+        <v>0.3812572014545543</v>
       </c>
       <c r="M9" t="n">
-        <v>2.60554711088801</v>
+        <v>2.642529942658157</v>
       </c>
       <c r="N9" t="n">
-        <v>12.06311719055383</v>
+        <v>12.51270262544577</v>
       </c>
       <c r="O9" t="n">
-        <v>3.473199848922291</v>
+        <v>3.53732987229715</v>
       </c>
       <c r="P9" t="n">
-        <v>351.1623202377515</v>
+        <v>351.0502209904527</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18750,28 +18848,28 @@
         <v>0.1184</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3104915878555122</v>
+        <v>0.3194083315189956</v>
       </c>
       <c r="J10" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3278638904907327</v>
+        <v>0.3361872625552477</v>
       </c>
       <c r="M10" t="n">
-        <v>2.637324068389688</v>
+        <v>2.670414517483962</v>
       </c>
       <c r="N10" t="n">
-        <v>11.22329928904338</v>
+        <v>11.51993161964871</v>
       </c>
       <c r="O10" t="n">
-        <v>3.35011929474808</v>
+        <v>3.394102476303376</v>
       </c>
       <c r="P10" t="n">
-        <v>348.4830148915514</v>
+        <v>348.3876415230072</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18809,7 +18907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K355"/>
+  <dimension ref="A1:K357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39047,6 +39145,120 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-35.44711357808224,174.42717736377534</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-35.44786751410207,174.42687664017834</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-35.44865478146279,174.42674103807624</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-35.44940439676928,174.42675957364605</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-35.45014417228019,174.426784875171</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-35.4508846357515,174.4268781683947</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-35.45161662376192,174.4270218442962</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-35.452312096011205,174.42735602032462</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-35.45300483587265,174.42762841025413</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-35.44711861012648,174.42718968536556</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-35.447872970870435,174.42689879356223</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-35.44865521278461,174.4267474061071</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-35.44940467555952,174.4267755446832</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-35.4501439424388,174.426809001018</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-35.45088379679561,174.42689145973856</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-35.4516141739276,174.427043674571</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-35.452302880898536,174.42739942386416</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-35.453001120326505,174.42764023869782</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
